--- a/data/trans_bre/P71_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P71_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 12,53</t>
+          <t>3,67; 12,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 2,55</t>
+          <t>-9,07; 2,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 4,64</t>
+          <t>-7,83; 4,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 13,73</t>
+          <t>-2,81; 14,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,17; 111,42</t>
+          <t>23,62; 112,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 10,32</t>
+          <t>-28,6; 10,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 17,86</t>
+          <t>-24,58; 17,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 155,11</t>
+          <t>-17,54; 151,26</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 9,22</t>
+          <t>-0,71; 8,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 8,96</t>
+          <t>-1,32; 9,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 3,49</t>
+          <t>-8,39; 2,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 43,18</t>
+          <t>0,74; 44,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 61,02</t>
+          <t>-4,24; 56,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 33,29</t>
+          <t>-4,43; 35,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 11,08</t>
+          <t>-22,2; 8,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 424,46</t>
+          <t>1,87; 429,02</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 14,85</t>
+          <t>6,11; 14,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 6,19</t>
+          <t>-4,64; 6,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 9,65</t>
+          <t>-0,95; 9,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 3,75</t>
+          <t>-5,04; 3,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,59; 116,64</t>
+          <t>34,58; 115,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 19,48</t>
+          <t>-12,56; 19,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 31,72</t>
+          <t>-2,54; 32,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 32,77</t>
+          <t>-31,0; 33,06</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 15,52</t>
+          <t>4,84; 15,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 6,21</t>
+          <t>-6,31; 5,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 8,91</t>
+          <t>-2,58; 9,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 11,85</t>
+          <t>0,35; 12,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,04; 118,75</t>
+          <t>25,9; 116,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 20,12</t>
+          <t>-16,77; 19,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 24,67</t>
+          <t>-6,22; 25,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 272,43</t>
+          <t>2,7; 300,71</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 11,72</t>
+          <t>-0,94; 11,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 5,48</t>
+          <t>-7,49; 5,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 9,72</t>
+          <t>-3,48; 9,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 6,76</t>
+          <t>-1,44; 6,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 56,15</t>
+          <t>-3,77; 56,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 20,87</t>
+          <t>-21,79; 19,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 31,61</t>
+          <t>-9,42; 29,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 44,46</t>
+          <t>-7,07; 42,29</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,8; 24,28</t>
+          <t>10,37; 24,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 11,58</t>
+          <t>-2,44; 11,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 9,48</t>
+          <t>-4,72; 9,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 3,34</t>
+          <t>-9,05; 3,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,96; 124,74</t>
+          <t>37,88; 126,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 63,3</t>
+          <t>-9,22; 59,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 37,02</t>
+          <t>-14,56; 34,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,56; 36,46</t>
+          <t>-75,69; 34,14</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 19,55</t>
+          <t>2,75; 19,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 11,85</t>
+          <t>-4,47; 11,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 15,08</t>
+          <t>-0,18; 14,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,34; 14,42</t>
+          <t>6,39; 14,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 74,18</t>
+          <t>6,32; 70,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 52,43</t>
+          <t>-13,88; 48,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 62,61</t>
+          <t>-0,55; 59,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,72; 208,12</t>
+          <t>54,67; 212,54</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,84; 11,97</t>
+          <t>7,68; 11,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,6</t>
+          <t>-1,25; 3,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,75</t>
+          <t>-0,07; 4,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,94</t>
+          <t>1,31; 10,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>40,78; 69,44</t>
+          <t>40,33; 69,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 12,28</t>
+          <t>-3,99; 11,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 14,86</t>
+          <t>-0,16; 14,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,46; 83,51</t>
+          <t>10,03; 95,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P71_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P71_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 12,62</t>
+          <t>2,96; 12,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 2,85</t>
+          <t>-9,07; 3,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 4,58</t>
+          <t>-6,95; 5,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 14,13</t>
+          <t>-6,49; 10,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,62; 112,44</t>
+          <t>18,19; 110,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 10,89</t>
+          <t>-29,69; 11,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 17,94</t>
+          <t>-21,52; 19,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 151,26</t>
+          <t>-31,55; 85,24</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,87</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>105,37%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 8,51</t>
+          <t>-0,7; 8,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 9,63</t>
+          <t>-1,67; 8,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 2,86</t>
+          <t>-8,25; 2,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 44,55</t>
+          <t>-2,36; 8,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 56,42</t>
+          <t>-3,81; 59,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 35,23</t>
+          <t>-4,97; 32,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 8,59</t>
+          <t>-22,33; 8,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 429,02</t>
+          <t>-14,16; 76,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,06%</t>
+          <t>-4,2%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 14,81</t>
+          <t>6,51; 15,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 6,46</t>
+          <t>-4,15; 5,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 9,73</t>
+          <t>-1,4; 9,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 3,78</t>
+          <t>-4,6; 3,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,58; 115,38</t>
+          <t>37,64; 114,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 19,73</t>
+          <t>-10,96; 18,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 32,99</t>
+          <t>-3,81; 31,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 33,06</t>
+          <t>-25,38; 24,01</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 15,5</t>
+          <t>5,06; 15,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 5,96</t>
+          <t>-5,55; 6,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 9,06</t>
+          <t>-2,13; 9,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 12,18</t>
+          <t>-2,71; 4,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,9; 116,36</t>
+          <t>27,09; 117,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 19,24</t>
+          <t>-15,24; 19,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 25,18</t>
+          <t>-5,09; 25,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 300,71</t>
+          <t>-15,64; 35,52</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 11,52</t>
+          <t>-0,96; 11,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 5,17</t>
+          <t>-6,77; 6,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 9,24</t>
+          <t>-4,18; 9,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,36</t>
+          <t>-1,9; 6,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 56,71</t>
+          <t>-3,22; 57,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 19,93</t>
+          <t>-20,29; 23,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 29,07</t>
+          <t>-10,8; 28,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 42,29</t>
+          <t>-8,92; 42,44</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-18,33%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,37; 24,28</t>
+          <t>10,17; 23,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 11,35</t>
+          <t>-2,93; 11,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 9,02</t>
+          <t>-4,31; 9,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 3,08</t>
+          <t>-1,35; 5,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,88; 126,13</t>
+          <t>38,3; 122,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 59,74</t>
+          <t>-11,16; 60,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 34,3</t>
+          <t>-13,58; 37,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,69; 34,14</t>
+          <t>-11,88; 64,3</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,57</t>
+          <t>11,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>120,42%</t>
+          <t>127,83%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 19,19</t>
+          <t>1,31; 19,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 11,03</t>
+          <t>-4,3; 11,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 14,81</t>
+          <t>0,12; 15,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,39; 14,1</t>
+          <t>7,45; 14,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 70,61</t>
+          <t>2,97; 70,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 48,61</t>
+          <t>-13,89; 47,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 59,69</t>
+          <t>0,18; 61,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,67; 212,54</t>
+          <t>66,88; 224,87</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,9</t>
+          <t>7,74; 11,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,31</t>
+          <t>-1,36; 3,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,59</t>
+          <t>-0,0; 4,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 10,0</t>
+          <t>0,99; 4,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>40,33; 69,85</t>
+          <t>41,09; 70,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 11,11</t>
+          <t>-4,36; 11,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 14,36</t>
+          <t>-0,12; 13,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,03; 95,2</t>
+          <t>6,37; 32,48</t>
         </is>
       </c>
     </row>
